--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C142"/>
+  <dimension ref="A1:C143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2266,6 +2266,19 @@
         <v>76</v>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>0</v>
+      </c>
+      <c r="C143" t="n">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C143"/>
+  <dimension ref="A1:C144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2279,6 +2279,19 @@
         <v>87</v>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>0</v>
+      </c>
+      <c r="C144" t="n">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C144"/>
+  <dimension ref="A1:C145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2292,6 +2292,19 @@
         <v>97</v>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>0</v>
+      </c>
+      <c r="C145" t="n">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C145"/>
+  <dimension ref="A1:C146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2305,6 +2305,19 @@
         <v>107</v>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>0</v>
+      </c>
+      <c r="C146" t="n">
+        <v>113</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C146"/>
+  <dimension ref="A1:C147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2318,6 +2318,19 @@
         <v>113</v>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>0</v>
+      </c>
+      <c r="C147" t="n">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C147"/>
+  <dimension ref="A1:C148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2331,6 +2331,19 @@
         <v>90</v>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>0</v>
+      </c>
+      <c r="C148" t="n">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C148"/>
+  <dimension ref="A1:C149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2344,6 +2344,19 @@
         <v>90</v>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>0</v>
+      </c>
+      <c r="C149" t="n">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C149"/>
+  <dimension ref="A1:C150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2357,6 +2357,19 @@
         <v>81</v>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>0</v>
+      </c>
+      <c r="C150" t="n">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C150"/>
+  <dimension ref="A1:C151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2370,6 +2370,19 @@
         <v>98</v>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>0</v>
+      </c>
+      <c r="C151" t="n">
+        <v>118</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C151"/>
+  <dimension ref="A1:C152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2383,6 +2383,19 @@
         <v>118</v>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>0</v>
+      </c>
+      <c r="C152" t="n">
+        <v>108</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C152"/>
+  <dimension ref="A1:C153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2396,6 +2396,19 @@
         <v>108</v>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>0</v>
+      </c>
+      <c r="C153" t="n">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C153"/>
+  <dimension ref="A1:C154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2409,6 +2409,19 @@
         <v>121</v>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>0</v>
+      </c>
+      <c r="C154" t="n">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C154"/>
+  <dimension ref="A1:C155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2422,6 +2422,19 @@
         <v>86</v>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>0</v>
+      </c>
+      <c r="C155" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C155"/>
+  <dimension ref="A1:C156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2435,6 +2435,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>0</v>
+      </c>
+      <c r="C156" t="n">
+        <v>95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C156"/>
+  <dimension ref="A1:C157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2448,6 +2448,19 @@
         <v>95</v>
       </c>
     </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>0</v>
+      </c>
+      <c r="C157" t="n">
+        <v>99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C157"/>
+  <dimension ref="A1:C158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2461,6 +2461,19 @@
         <v>99</v>
       </c>
     </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>0</v>
+      </c>
+      <c r="C158" t="n">
+        <v>135</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C158"/>
+  <dimension ref="A1:C159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2474,6 +2474,19 @@
         <v>135</v>
       </c>
     </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>0</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C159"/>
+  <dimension ref="A1:C160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2487,6 +2487,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>0</v>
+      </c>
+      <c r="C160" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C160"/>
+  <dimension ref="A1:C161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2500,6 +2500,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>0</v>
+      </c>
+      <c r="C161" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C161"/>
+  <dimension ref="A1:C162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2513,6 +2513,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>0</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C162"/>
+  <dimension ref="A1:C163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2526,6 +2526,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>0</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C163"/>
+  <dimension ref="A1:C164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2539,6 +2539,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>0</v>
+      </c>
+      <c r="C164" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C164"/>
+  <dimension ref="A1:C165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2552,6 +2552,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>0</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C165"/>
+  <dimension ref="A1:C166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2565,6 +2565,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>0</v>
+      </c>
+      <c r="C166" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C166"/>
+  <dimension ref="A1:C167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2578,6 +2578,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>0</v>
+      </c>
+      <c r="C167" t="n">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C167"/>
+  <dimension ref="A1:C168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2591,6 +2591,19 @@
         <v>107</v>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>0</v>
+      </c>
+      <c r="C168" t="n">
+        <v>117</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C168"/>
+  <dimension ref="A1:C169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2604,6 +2604,19 @@
         <v>117</v>
       </c>
     </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>0</v>
+      </c>
+      <c r="C169" t="n">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C169"/>
+  <dimension ref="A1:C170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2617,6 +2617,19 @@
         <v>87</v>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>0</v>
+      </c>
+      <c r="C170" t="n">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C170"/>
+  <dimension ref="A1:C171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2630,6 +2630,19 @@
         <v>97</v>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>0</v>
+      </c>
+      <c r="C171" t="n">
+        <v>125</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C171"/>
+  <dimension ref="A1:C172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2643,6 +2643,19 @@
         <v>125</v>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>0</v>
+      </c>
+      <c r="C172" t="n">
+        <v>115</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C172"/>
+  <dimension ref="A1:C173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2656,6 +2656,19 @@
         <v>115</v>
       </c>
     </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>0</v>
+      </c>
+      <c r="C173" t="n">
+        <v>113</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C173"/>
+  <dimension ref="A1:C174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2669,6 +2669,19 @@
         <v>113</v>
       </c>
     </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>0</v>
+      </c>
+      <c r="C174" t="n">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C174"/>
+  <dimension ref="A1:C175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2682,6 +2682,19 @@
         <v>106</v>
       </c>
     </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>0</v>
+      </c>
+      <c r="C175" t="n">
+        <v>116</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C175"/>
+  <dimension ref="A1:C176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2695,6 +2695,19 @@
         <v>116</v>
       </c>
     </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>0</v>
+      </c>
+      <c r="C176" t="n">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C176"/>
+  <dimension ref="A1:C177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2708,6 +2708,19 @@
         <v>110</v>
       </c>
     </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>0</v>
+      </c>
+      <c r="C177" t="n">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C177"/>
+  <dimension ref="A1:C178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2721,6 +2721,19 @@
         <v>103</v>
       </c>
     </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>0</v>
+      </c>
+      <c r="C178" t="n">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C178"/>
+  <dimension ref="A1:C179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2734,6 +2734,19 @@
         <v>123</v>
       </c>
     </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>0</v>
+      </c>
+      <c r="C179" t="n">
+        <v>148</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C179"/>
+  <dimension ref="A1:C180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2747,6 +2747,19 @@
         <v>148</v>
       </c>
     </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>0</v>
+      </c>
+      <c r="C180" t="n">
+        <v>168</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C180"/>
+  <dimension ref="A1:C181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2760,6 +2760,19 @@
         <v>168</v>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>0</v>
+      </c>
+      <c r="C181" t="n">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C181"/>
+  <dimension ref="A1:C182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2773,6 +2773,19 @@
         <v>104</v>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>0</v>
+      </c>
+      <c r="C182" t="n">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C182"/>
+  <dimension ref="A1:C183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2786,6 +2786,19 @@
         <v>85</v>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>0</v>
+      </c>
+      <c r="C183" t="n">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C183"/>
+  <dimension ref="A1:C186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2799,6 +2799,45 @@
         <v>92</v>
       </c>
     </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>0</v>
+      </c>
+      <c r="C184" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>0</v>
+      </c>
+      <c r="C185" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>0</v>
+      </c>
+      <c r="C186" t="n">
+        <v>141</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C186"/>
+  <dimension ref="A1:C187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2838,6 +2838,19 @@
         <v>141</v>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>0</v>
+      </c>
+      <c r="C187" t="n">
+        <v>163</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C187"/>
+  <dimension ref="A1:C188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2851,6 +2851,19 @@
         <v>163</v>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>0</v>
+      </c>
+      <c r="C188" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C188"/>
+  <dimension ref="A1:C189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2864,6 +2864,19 @@
         <v>1</v>
       </c>
     </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>0</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C189"/>
+  <dimension ref="A1:C190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2877,6 +2877,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>0</v>
+      </c>
+      <c r="C190" t="n">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C190"/>
+  <dimension ref="A1:C191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2890,6 +2890,19 @@
         <v>107</v>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>0</v>
+      </c>
+      <c r="C191" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
